--- a/docs/assets/cases/days-employed-special.xlsx
+++ b/docs/assets/cases/days-employed-special.xlsx
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"55ac7f0c-2773-4f52-9085-75415347e4be"</t>
+          <t>"7eed8cf6-c27a-44bd-a134-b8d22192e3ae"</t>
         </is>
       </c>
       <c r="C3" t="n">

--- a/docs/assets/cases/days-employed-special.xlsx
+++ b/docs/assets/cases/days-employed-special.xlsx
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"7eed8cf6-c27a-44bd-a134-b8d22192e3ae"</t>
+          <t>"ac85fb2a-41da-4d18-a94e-c7bfdd955b12"</t>
         </is>
       </c>
       <c r="C3" t="n">
